--- a/Result/profitability/3285.xlsx
+++ b/Result/profitability/3285.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0.23875</v>
+        <v>0.305</v>
       </c>
       <c r="N2" t="n">
-        <v>22.7675</v>
+        <v>23.43625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.99</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34625</v>
+        <v>0.3725</v>
       </c>
       <c r="N3" t="n">
-        <v>22.99625</v>
+        <v>23.255</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0.31875</v>
+        <v>0.39875</v>
       </c>
       <c r="N4" t="n">
-        <v>22.905</v>
+        <v>23.35875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>0.365</v>
+        <v>0.47875</v>
       </c>
       <c r="N5" t="n">
-        <v>23.11375</v>
+        <v>23.63125</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>98.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5774999999999999</v>
+        <v>0.5912500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>23.8275</v>
+        <v>23.27375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5962499999999999</v>
+        <v>0.63125</v>
       </c>
       <c r="N7" t="n">
-        <v>23.71375</v>
+        <v>23.12875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.55125</v>
+        <v>0.60125</v>
       </c>
       <c r="N8" t="n">
-        <v>22.765</v>
+        <v>22.73125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9199,6 +9199,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3285</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>337</v>
+      </c>
+      <c r="D70" t="n">
+        <v>256</v>
+      </c>
+      <c r="E70" t="n">
+        <v>81</v>
+      </c>
+      <c r="F70" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="G70" t="n">
+        <v>28</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>8.20%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>9</v>
+      </c>
+      <c r="J70" t="n">
+        <v>37</v>
+      </c>
+      <c r="K70" t="n">
+        <v>28</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="N70" t="n">
+        <v>23.20375</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1.538461538461538</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>-0.2699999999999996</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-0.01115702479338843</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>4.140000000000001</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.2091965639211724</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
